--- a/LSTM_Transformer/stft_ablation_WAVELET.xlsx
+++ b/LSTM_Transformer/stft_ablation_WAVELET.xlsx
@@ -498,28 +498,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9853</v>
+        <v>0.5204</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.5385</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.2143</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8889</v>
+        <v>0.5385</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.3571</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.7857</v>
       </c>
     </row>
   </sheetData>
